--- a/Use_cases/field_testing/DiCamillo_field_testing_asmr/DiCamillo_field_testing_asmr.xlsx
+++ b/Use_cases/field_testing/DiCamillo_field_testing_asmr/DiCamillo_field_testing_asmr.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://univpm-my.sharepoint.com/personal/s1116344_pm_univpm_it/Documents/PhD/ASMR/Use_cases/ASMR_Gioia/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\claud\Documents\COMUNE\STUDIO_LAVORO\Data_analysis\Projects\ASMR\Use_cases\field_testing\DiCamillo_field_testing_asmr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="639" documentId="8_{EFAEFAC3-690E-4DEC-BEA6-F06FAFF8170D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F788F278-CEDD-4C3A-9A43-2CDBC75F8C4A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ED7BCF5-ED49-4923-9801-070793C0975D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{AFBFBA82-9AEE-4DB2-BCE9-4DEFE9217D81}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="10" activeTab="16" xr2:uid="{AFBFBA82-9AEE-4DB2-BCE9-4DEFE9217D81}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="25" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="306">
   <si>
     <t>The templates were generated using the ASMR checklist version of;</t>
   </si>
@@ -239,9 +239,6 @@
     <t>eventDate</t>
   </si>
   <si>
-    <t>UTC</t>
-  </si>
-  <si>
     <t>eventDurationValue</t>
   </si>
   <si>
@@ -269,9 +266,6 @@
     <t>2026-07</t>
   </si>
   <si>
-    <t>+02:00</t>
-  </si>
-  <si>
     <t>P4D</t>
   </si>
   <si>
@@ -878,9 +872,6 @@
     <t>Photographic census</t>
   </si>
   <si>
-    <t>Visual census based on three replicate 1-minute video transects (1 m width) performed at 5-10 m 15-20 m and 30-35 m depth. Video surveys were conducted across seven sites and three depth ranges using 5 m × 1 m belt transects. Transects were surveyed at a standardized swimming speed to ensure consistent sampling effort. A total of 21 transects were completed, corresponding to a total surveyed area of 105 m^2. Occurrence of charismatic alien invasive marine species was assessed from video recordings</t>
-  </si>
-  <si>
     <t>Marine Ecoregions of the World (MEOW)</t>
   </si>
   <si>
@@ -953,24 +944,12 @@
     <t>meter</t>
   </si>
   <si>
-    <t>NA?</t>
-  </si>
-  <si>
-    <t>2 lights xxxx</t>
-  </si>
-  <si>
-    <t>3 lights xxxx</t>
-  </si>
-  <si>
     <t>Olympus Tough TG-6 with Weefine underwater housing</t>
   </si>
   <si>
     <t>GoPro HERO11 Black</t>
   </si>
   <si>
-    <t>1 m</t>
-  </si>
-  <si>
     <t>opportunisticSearch|restrictedSearch</t>
   </si>
   <si>
@@ -986,12 +965,6 @@
     <t>Census conducted both inside and outside the transects MT1_KZ_ChAIMar. Organism size was estimated from underwater photographs acquired with a calliper placed next to the specimen and measured through digital image processing</t>
   </si>
   <si>
-    <t>non avendo fatto dei photoquadrats standardizzati non li includerei nel computo dell'area campionata</t>
-  </si>
-  <si>
-    <t>si tratta di foto casuali degli organismi target</t>
-  </si>
-  <si>
     <t>PT50M</t>
   </si>
   <si>
@@ -1001,15 +974,6 @@
     <t>PT55M</t>
   </si>
   <si>
-    <t>somma dei survey? 361 minuti?</t>
-  </si>
-  <si>
-    <t>per ogni profondità ci sono 3 repliche. aggiungo?</t>
-  </si>
-  <si>
-    <t>è lo stesso perchè c'era anche il VC</t>
-  </si>
-  <si>
     <t>Palinurus elephas|Hermodice carunculata|Centrostephanus tenuispinus | Charonia triton|Muraena helena|Sparisoma cretense|Ephinephelus marginatus|Pterois miles|Dactylopteris volitans|Scorpaena scrofa</t>
   </si>
   <si>
@@ -1020,6 +984,25 @@
   </si>
   <si>
     <t>Università Politecnica delle Marche</t>
+  </si>
+  <si>
+    <t>None</t>
+  </si>
+  <si>
+    <t>2 x V3Kv2 video light
+SUPE Scubalamp V3Kv2 Moive grade COB LED Photo/Video Light - 5,000 lumens</t>
+  </si>
+  <si>
+    <t>Visual census based on three replicate 1-minute video transects (1 m width) performed at 5-10 m 15-20 m and 30-35 m depth. Video surveys were conducted across seven sites and three depth ranges using 5 m × 1 m belt transects. Transects were surveyed at a standardized swimming speed to ensure consistent sampling effort. A total of 21 transects were completed, corresponding to a total surveyed area of 105 m^2. Occurrence of charismatic, alien, and invasive marine species was assessed from video recordings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NIS species abundance </t>
+  </si>
+  <si>
+    <t>Species abundances</t>
+  </si>
+  <si>
+    <t>Benthic invertebrates Abundance and distribution | Fish Abundance and distribution</t>
   </si>
 </sst>
 </file>
@@ -1029,7 +1012,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1060,13 +1043,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="3" tint="0.249977111117893"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -1077,13 +1053,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1147,15 +1116,17 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="46" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="46" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="46" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1581,7 +1552,7 @@
     <col min="7" max="7" width="27.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="28.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="30.5546875" style="2" customWidth="1"/>
     <col min="11" max="11" width="14" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="15.6640625" customWidth="1"/>
@@ -1598,7 +1569,7 @@
   <sheetData>
     <row r="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -1607,185 +1578,191 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="V1" s="3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:22" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F2" t="s">
+        <v>249</v>
+      </c>
+      <c r="G2" t="s">
+        <v>250</v>
+      </c>
+      <c r="H2" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="I2" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="J2" s="23" t="s">
+        <v>301</v>
+      </c>
+      <c r="K2" s="21" t="s">
+        <v>287</v>
+      </c>
+      <c r="L2" t="s">
         <v>253</v>
       </c>
-      <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" t="s">
-        <v>251</v>
-      </c>
-      <c r="G2" t="s">
-        <v>252</v>
-      </c>
-      <c r="H2" s="21" t="s">
-        <v>289</v>
-      </c>
-      <c r="I2" s="21" t="s">
-        <v>287</v>
-      </c>
-      <c r="J2" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>293</v>
-      </c>
-      <c r="L2" t="s">
-        <v>255</v>
-      </c>
       <c r="M2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="P2" t="s">
+        <v>259</v>
       </c>
       <c r="Q2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="S2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="U2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="V2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D3" t="s">
+        <v>248</v>
+      </c>
+      <c r="E3" t="s">
+        <v>121</v>
+      </c>
+      <c r="F3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G3" t="s">
         <v>250</v>
       </c>
-      <c r="E3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F3" t="s">
-        <v>251</v>
-      </c>
-      <c r="G3" t="s">
-        <v>252</v>
-      </c>
       <c r="H3" s="21" t="s">
+        <v>283</v>
+      </c>
+      <c r="I3" s="21" t="s">
+        <v>285</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>253</v>
+      </c>
+      <c r="K3" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="I3" s="21" t="s">
-        <v>288</v>
-      </c>
-      <c r="J3" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="K3" s="21" t="s">
-        <v>292</v>
-      </c>
       <c r="L3" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="M3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="N3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="O3" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="P3" t="s">
+        <v>259</v>
       </c>
       <c r="Q3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="R3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="S3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="T3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="U3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="V3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -1822,7 +1799,7 @@
   <sheetData>
     <row r="1" spans="1:20" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -1831,78 +1808,75 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="17" t="s">
+        <v>290</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="O1" s="20" t="s">
-        <v>297</v>
-      </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>197</v>
-      </c>
-      <c r="S1" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="T1" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>264</v>
+        <v>302</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H2" t="b">
         <v>0</v>
@@ -1911,45 +1885,45 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>123</v>
-      </c>
-      <c r="K2" s="21" t="s">
-        <v>294</v>
+        <v>121</v>
+      </c>
+      <c r="K2" s="21">
+        <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M2" t="s">
-        <v>255</v>
-      </c>
-      <c r="N2" s="21">
+        <v>253</v>
+      </c>
+      <c r="N2" s="18">
         <v>0</v>
       </c>
-      <c r="O2" s="22" t="s">
-        <v>108</v>
-      </c>
-      <c r="P2" s="21" t="s">
-        <v>296</v>
+      <c r="O2" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="P2" s="18" t="s">
+        <v>289</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>261</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="F3" t="s">
         <v>254</v>
       </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="D3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>299</v>
-      </c>
-      <c r="F3" t="s">
-        <v>256</v>
-      </c>
       <c r="G3" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H3" t="b">
         <v>0</v>
@@ -1958,25 +1932,25 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="K3" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="L3" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="M3" t="s">
-        <v>255</v>
-      </c>
-      <c r="N3" s="21">
+        <v>253</v>
+      </c>
+      <c r="N3" s="18">
         <v>0</v>
       </c>
-      <c r="O3" s="22" t="s">
-        <v>298</v>
-      </c>
-      <c r="P3" s="21" t="s">
-        <v>295</v>
+      <c r="O3" s="19" t="s">
+        <v>291</v>
+      </c>
+      <c r="P3" s="18" t="s">
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -2010,63 +1984,63 @@
   <sheetData>
     <row r="1" spans="1:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>212</v>
-      </c>
-      <c r="P1" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
         <v>58</v>
-      </c>
-      <c r="B2" t="s">
-        <v>59</v>
       </c>
       <c r="C2" t="s">
         <v>33</v>
@@ -2078,22 +2052,22 @@
         <v>21</v>
       </c>
       <c r="F2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="J2" s="21">
         <v>105</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="M2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="N2" t="b">
         <v>1</v>
@@ -2101,78 +2075,48 @@
       <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" s="22">
+      <c r="P2" s="24">
         <v>361</v>
       </c>
-      <c r="Q2" s="22">
+      <c r="Q2" s="24">
         <v>361</v>
       </c>
-      <c r="R2" s="19" t="s">
-        <v>307</v>
-      </c>
+      <c r="R2" s="24"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="J3" s="19" t="s">
-        <v>300</v>
-      </c>
+      <c r="A3" s="16"/>
+      <c r="J3" s="16"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="J4" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="P4" s="19" t="s">
-        <v>305</v>
-      </c>
+      <c r="J4" s="16"/>
+      <c r="P4" s="16"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P5" s="20" t="s">
-        <v>52</v>
-      </c>
+      <c r="P5" s="17"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P6" s="19" t="s">
-        <v>62</v>
-      </c>
+      <c r="P6" s="16"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P7" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q7">
-        <f>51+50+53+50+51+51+55</f>
-        <v>361</v>
-      </c>
+      <c r="P7" s="20"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P8" s="24" t="s">
-        <v>302</v>
-      </c>
+      <c r="P8" s="20"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P9" s="24" t="s">
-        <v>303</v>
-      </c>
+      <c r="P9" s="20"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P10" s="24" t="s">
-        <v>302</v>
-      </c>
+      <c r="P10" s="20"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P11" s="24" t="s">
-        <v>66</v>
-      </c>
+      <c r="P11" s="20"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P12" s="24" t="s">
-        <v>66</v>
-      </c>
+      <c r="P12" s="20"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="P13" s="24" t="s">
-        <v>304</v>
-      </c>
+      <c r="P13" s="20"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -2184,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F29E1CE-6F0A-4720-B825-D88B9C03E178}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -2196,7 +2140,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -2205,21 +2149,38 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>251</v>
+      </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>254</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" t="s">
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -2229,7 +2190,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C0C21D1-1228-4F44-AA26-947BF92BFA1B}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.109375" customWidth="1"/>
@@ -2245,7 +2206,7 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -2254,51 +2215,81 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>225</v>
       </c>
       <c r="J1" s="3"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>251</v>
+      </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="F2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="H2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="I2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>252</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="3"/>
+      <c r="D3" t="s">
+        <v>254</v>
+      </c>
+      <c r="E3" t="s">
+        <v>254</v>
+      </c>
+      <c r="F3" t="s">
+        <v>254</v>
+      </c>
+      <c r="G3" t="s">
+        <v>254</v>
+      </c>
+      <c r="H3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I3" t="s">
+        <v>254</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2336,7 +2327,7 @@
   <sheetData>
     <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -2345,33 +2336,33 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>
@@ -2396,7 +2387,7 @@
   <sheetData>
     <row r="1" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>47</v>
@@ -2405,62 +2396,62 @@
         <v>48</v>
       </c>
       <c r="D1" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="H3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="I3" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2473,12 +2464,12 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6640625" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="31.5546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="31.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.44140625" customWidth="1"/>
     <col min="7" max="7" width="24.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="28" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="23" bestFit="1" customWidth="1"/>
@@ -2494,42 +2485,63 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>244</v>
-      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
       <c r="C2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>121</v>
+      </c>
+      <c r="F2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G2" t="s">
+        <v>300</v>
+      </c>
+      <c r="H2" t="s">
+        <v>304</v>
+      </c>
+      <c r="I2" t="s">
+        <v>305</v>
+      </c>
+      <c r="J2" t="s">
+        <v>300</v>
+      </c>
+      <c r="K2" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -2549,7 +2561,7 @@
     <col min="5" max="5" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="42.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="100.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2578,7 +2590,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>20</v>
       </c>
@@ -2600,7 +2612,7 @@
       <c r="G2" t="s">
         <v>23</v>
       </c>
-      <c r="H2" t="s">
+      <c r="H2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
@@ -2663,7 +2675,7 @@
     </row>
     <row r="2" spans="1:19" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
-        <v>310</v>
+        <v>298</v>
       </c>
       <c r="B2" s="11" t="s">
         <v>22</v>
@@ -2675,7 +2687,7 @@
         <v>35</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>309</v>
+        <v>297</v>
       </c>
       <c r="F2" s="10" t="s">
         <v>36</v>
@@ -2728,8 +2740,8 @@
   <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12.5546875" customWidth="1"/>
-    <col min="2" max="2" width="28.109375" customWidth="1"/>
+    <col min="1" max="1" width="20.6640625" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" customWidth="1"/>
     <col min="3" max="3" width="12.44140625" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.5546875" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
@@ -2781,7 +2793,7 @@
         <v>46</v>
       </c>
       <c r="B2" t="s">
-        <v>311</v>
+        <v>299</v>
       </c>
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
@@ -2821,23 +2833,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80ADC85F-3A32-47EA-B2E0-CFC389B02588}">
-  <dimension ref="A1:L30"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="40.33203125" customWidth="1"/>
+    <col min="1" max="1" width="45.77734375" customWidth="1"/>
     <col min="2" max="2" width="34.5546875" customWidth="1"/>
     <col min="3" max="3" width="13.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="31.5546875" style="8" customWidth="1"/>
-    <col min="5" max="5" width="29.6640625" style="16" customWidth="1"/>
-    <col min="6" max="6" width="21" style="16" customWidth="1"/>
-    <col min="7" max="7" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="26.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>47</v>
       </c>
@@ -2850,478 +2860,416 @@
       <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="17" t="s">
+      <c r="E1" s="3" t="s">
         <v>51</v>
       </c>
+      <c r="F1" s="3" t="s">
+        <v>52</v>
+      </c>
       <c r="G1" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="K1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="C2" t="s">
+      <c r="E2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" t="s">
+        <v>61</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" t="s">
+        <v>244</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F3" t="s">
+        <v>65</v>
+      </c>
+      <c r="G3" s="8">
+        <v>46222</v>
+      </c>
+      <c r="H3" s="13">
+        <v>0.41736111111111113</v>
+      </c>
+      <c r="I3" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>244</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="F4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G4" s="8">
+        <v>46222</v>
+      </c>
+      <c r="H4" s="13">
+        <v>0.54652777777777772</v>
+      </c>
+      <c r="I4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C5" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>294</v>
+      </c>
+      <c r="F5" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="8">
+        <v>46223</v>
+      </c>
+      <c r="H5" s="13">
+        <v>0.39861111111111114</v>
+      </c>
+      <c r="I5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="F6" t="s">
+        <v>65</v>
+      </c>
+      <c r="G6" s="8">
+        <v>46223</v>
+      </c>
+      <c r="H6" s="13">
+        <v>0.5493055555555556</v>
+      </c>
+      <c r="I6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" t="s">
+        <v>244</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F7" t="s">
+        <v>65</v>
+      </c>
+      <c r="G7" s="8">
+        <v>46224</v>
+      </c>
+      <c r="H7" s="13">
+        <v>0.3527777777777778</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F8" t="s">
+        <v>65</v>
+      </c>
+      <c r="G8" s="8">
+        <v>46225</v>
+      </c>
+      <c r="H8" s="13">
+        <v>0.40486111111111112</v>
+      </c>
+      <c r="I8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>73</v>
+      </c>
+      <c r="B9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G9" s="8">
+        <v>46225</v>
+      </c>
+      <c r="H9" s="13">
+        <v>0.52777777777777779</v>
+      </c>
+      <c r="I9" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>245</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E2" s="19"/>
-      <c r="F2" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="B10" t="s">
         <v>62</v>
       </c>
-      <c r="H2" t="s">
-        <v>63</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="J2" s="13"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" t="s">
-        <v>246</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E3" s="19" t="str">
-        <f>TEXT(I3,"yyyy-mm-dd")&amp;"T"&amp;TEXT(J3,"hh:mm")&amp;(F3)</f>
-        <v>yyyy-07-ddT10:01+02:00</v>
-      </c>
-      <c r="F3" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H3" t="s">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>265</v>
+      </c>
+      <c r="B13" t="s">
         <v>67</v>
       </c>
-      <c r="I3" s="8">
-        <v>46222</v>
-      </c>
-      <c r="J3" s="13">
-        <v>0.41736111111111113</v>
-      </c>
-      <c r="K3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>275</v>
+      </c>
+      <c r="B15" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>266</v>
+      </c>
+      <c r="B16" t="s">
         <v>69</v>
-      </c>
-      <c r="B4" t="s">
-        <v>59</v>
-      </c>
-      <c r="C4" t="s">
-        <v>246</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>70</v>
-      </c>
-      <c r="E4" s="19" t="str">
-        <f t="shared" ref="E4:E9" si="0">TEXT(I4,"yyyy-mm-dd")&amp;"T"&amp;TEXT(J4,"hh:mm")&amp;(F4)</f>
-        <v>yyyy-07-ddT13:07+02:00</v>
-      </c>
-      <c r="F4" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="H4" t="s">
-        <v>67</v>
-      </c>
-      <c r="I4" s="8">
-        <v>46222</v>
-      </c>
-      <c r="J4" s="13">
-        <v>0.54652777777777772</v>
-      </c>
-      <c r="K4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>yyyy-07-ddT09:34+02:00</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5" s="15" t="s">
-        <v>303</v>
-      </c>
-      <c r="H5" t="s">
-        <v>67</v>
-      </c>
-      <c r="I5" s="8">
-        <v>46223</v>
-      </c>
-      <c r="J5" s="13">
-        <v>0.39861111111111114</v>
-      </c>
-      <c r="K5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
-        <v>72</v>
-      </c>
-      <c r="B6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E6" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>yyyy-07-ddT13:11+02:00</v>
-      </c>
-      <c r="F6" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6" s="15" t="s">
-        <v>302</v>
-      </c>
-      <c r="H6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I6" s="8">
-        <v>46223</v>
-      </c>
-      <c r="J6" s="13">
-        <v>0.5493055555555556</v>
-      </c>
-      <c r="K6" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C7" t="s">
-        <v>246</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E7" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>yyyy-07-ddT08:28+02:00</v>
-      </c>
-      <c r="F7" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I7" s="8">
-        <v>46224</v>
-      </c>
-      <c r="J7" s="13">
-        <v>0.3527777777777778</v>
-      </c>
-      <c r="K7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
-        <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" t="s">
-        <v>246</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E8" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>yyyy-07-ddT09:43+02:00</v>
-      </c>
-      <c r="F8" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" t="s">
-        <v>67</v>
-      </c>
-      <c r="I8" s="8">
-        <v>46225</v>
-      </c>
-      <c r="J8" s="13">
-        <v>0.40486111111111112</v>
-      </c>
-      <c r="K8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>75</v>
-      </c>
-      <c r="B9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C9" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="E9" s="19" t="str">
-        <f t="shared" si="0"/>
-        <v>yyyy-07-ddT12:40+02:00</v>
-      </c>
-      <c r="F9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9" s="15" t="s">
-        <v>304</v>
-      </c>
-      <c r="H9" t="s">
-        <v>67</v>
-      </c>
-      <c r="I9" s="8">
-        <v>46225</v>
-      </c>
-      <c r="J9" s="13">
-        <v>0.52777777777777779</v>
-      </c>
-      <c r="K9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="E11" s="19"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>267</v>
-      </c>
-      <c r="B12" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>268</v>
-      </c>
-      <c r="B13" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>273</v>
-      </c>
-      <c r="B14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>278</v>
-      </c>
-      <c r="B15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>269</v>
-      </c>
-      <c r="B16" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="B18" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="B19" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="B20" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="B21" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="B22" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B23" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="B26" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="B27" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B28" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="B29" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="B30" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -3344,7 +3292,7 @@
     <col min="8" max="8" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="16.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="25.6640625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="22" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="23.88671875" bestFit="1" customWidth="1"/>
@@ -3383,138 +3331,138 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="K1" s="20" t="s">
+      <c r="M1" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="U1" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="V1" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="U1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="V1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="Y1" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Z1" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="Y1" s="3" t="s">
+      <c r="AA1" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="Z1" s="3" t="s">
+      <c r="AB1" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AC1" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AB1" s="3" t="s">
+      <c r="AD1" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AC1" s="3" t="s">
+      <c r="AE1" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="AD1" s="3" t="s">
+      <c r="AF1" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AE1" s="3" t="s">
+      <c r="AG1" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AF1" s="3" t="s">
+      <c r="AH1" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AG1" s="3" t="s">
+      <c r="AI1" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="AH1" s="3" t="s">
+      <c r="AJ1" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AI1" s="3" t="s">
+      <c r="AK1" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AJ1" s="3" t="s">
+      <c r="AL1" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AK1" s="3" t="s">
+      <c r="AM1" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AL1" s="3" t="s">
+      <c r="AN1" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AO1" s="3" t="s">
         <v>112</v>
-      </c>
-      <c r="AN1" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="AO1" s="3" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="2" spans="1:41" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F2">
         <v>43.043059999999997</v>
@@ -3529,51 +3477,51 @@
         <v>16.093060000000001</v>
       </c>
       <c r="J2" t="s">
+        <v>115</v>
+      </c>
+      <c r="K2" s="22" t="s">
+        <v>116</v>
+      </c>
+      <c r="N2" t="s">
+        <v>114</v>
+      </c>
+      <c r="R2" t="s">
         <v>117</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="S2" t="s">
         <v>118</v>
       </c>
-      <c r="N2" t="s">
-        <v>116</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="U2" t="s">
         <v>119</v>
       </c>
-      <c r="S2" t="s">
+      <c r="V2" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="T2" s="21" t="s">
-        <v>265</v>
-      </c>
-      <c r="U2" t="s">
+      <c r="AC2" t="s">
         <v>121</v>
       </c>
-      <c r="V2" s="6" t="s">
-        <v>122</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>123</v>
-      </c>
       <c r="AD2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F3">
         <v>43.059193999999998</v>
@@ -3588,40 +3536,40 @@
         <v>1.6052299999999999</v>
       </c>
       <c r="J3" t="s">
-        <v>117</v>
-      </c>
-      <c r="K3" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K3" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="V3" s="6"/>
       <c r="AC3" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD3" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="4" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F4">
         <v>43.053539999999998</v>
@@ -3636,40 +3584,40 @@
         <v>16.038080999999998</v>
       </c>
       <c r="J4" t="s">
-        <v>117</v>
-      </c>
-      <c r="K4" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="K4" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="N4" t="s">
         <v>125</v>
-      </c>
-      <c r="N4" t="s">
-        <v>127</v>
       </c>
       <c r="V4" s="6"/>
       <c r="AC4" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE4" t="s">
         <v>128</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="5" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F5">
         <v>43.007120999999998</v>
@@ -3684,40 +3632,40 @@
         <v>16.066808000000002</v>
       </c>
       <c r="J5" t="s">
-        <v>117</v>
-      </c>
-      <c r="K5" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K5" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="V5" s="6"/>
       <c r="AC5" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD5" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE5" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F6">
         <v>43.009689000000002</v>
@@ -3732,40 +3680,40 @@
         <v>16.068348</v>
       </c>
       <c r="J6" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K6" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N6" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="V6" s="6"/>
       <c r="AC6" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD6" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE6" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F7">
         <v>43.053545</v>
@@ -3780,40 +3728,40 @@
         <v>16.039752</v>
       </c>
       <c r="J7" t="s">
-        <v>117</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K7" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="V7" s="6"/>
       <c r="AC7" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD7" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE7" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="E8" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F8">
         <v>43.007120999999998</v>
@@ -3828,40 +3776,40 @@
         <v>16.066808000000002</v>
       </c>
       <c r="J8" t="s">
-        <v>117</v>
-      </c>
-      <c r="K8" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K8" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="V8" s="6"/>
       <c r="AC8" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE8" t="s">
         <v>128</v>
-      </c>
-      <c r="AD8" t="s">
-        <v>129</v>
-      </c>
-      <c r="AE8" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C9" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="F9">
         <v>43.004885000000002</v>
@@ -3876,23 +3824,23 @@
         <v>16.071550999999999</v>
       </c>
       <c r="J9" t="s">
-        <v>117</v>
-      </c>
-      <c r="K9" s="19" t="s">
-        <v>125</v>
+        <v>115</v>
+      </c>
+      <c r="K9" s="22" t="s">
+        <v>123</v>
       </c>
       <c r="N9" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="V9" s="6"/>
       <c r="AC9" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AD9" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AE9" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:41" x14ac:dyDescent="0.3">
@@ -3959,45 +3907,45 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="D2" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="E2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="G2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="H2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -4042,42 +3990,42 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="L1" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:12" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C2" t="s">
-        <v>308</v>
+        <v>58</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>296</v>
       </c>
     </row>
   </sheetData>
@@ -4115,43 +4063,43 @@
         <v>48</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="K1" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="N1" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="O1" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
